--- a/Bon_commande_robot-maker.xlsx
+++ b/Bon_commande_robot-maker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gokay\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gokay\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD79A862-B1A3-42AA-B207-47837CBE1A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3827BA3-7B86-4701-B5DD-E8B878D8AB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{CDB22E69-6756-4659-B8CD-4D80713F33EA}"/>
   </bookViews>
@@ -550,15 +550,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF32E24-AA5F-4298-AD6C-129A5A3C1A54}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -574,34 +574,32 @@
       <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>10</v>
       </c>
@@ -611,40 +609,29 @@
       <c r="E4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4">
+      <c r="F4" s="4">
         <v>1</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="K4">
+      <c r="I4">
         <v>8.4</v>
       </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
       <c r="L4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="E4:F4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>